--- a/docs/resources/mailing_list.xlsx
+++ b/docs/resources/mailing_list.xlsx
@@ -1,26 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
-  <workbookPr defaultThemeVersion="202300"/>
+<workbook xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2" conformance="strict">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
+  <workbookPr dateCompatibility="0" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/milesshultz/Documents/kings website/rock/resources/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/milesshultz/Documents/kings_website/rock/docs/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{0F1ECDD1-8F26-2A4A-9FB9-E9EEEBB9AC02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{30C6D1EF-AB46-2948-BD17-DD8C503A3731}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5180" yWindow="1880" windowWidth="28040" windowHeight="17180" xr2:uid="{9CD2B613-7F63-5943-BBFD-11025AF00D59}"/>
+    <workbookView xWindow="5580" yWindow="2380" windowWidth="27640" windowHeight="16680" xr2:uid="{DA709F05-24F1-A741-ABB1-68CCE26981F7}"/>
   </bookViews>
   <sheets>
-    <sheet name="1778783296_187467873853113354_s" sheetId="1" r:id="rId1"/>
+    <sheet name="1781904772_190740977600693589_s" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
+      <x14:workbookPr/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="10">
+<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="19" uniqueCount="14">
   <si>
     <t>Subscriber</t>
   </si>
@@ -40,10 +56,22 @@
     <t>Location</t>
   </si>
   <si>
+    <t>monicagchavez@gmail.com</t>
+  </si>
+  <si>
+    <t>United States</t>
+  </si>
+  <si>
+    <t>rachel.chasse21@gmail.com</t>
+  </si>
+  <si>
+    <t>steve@484farm.com</t>
+  </si>
+  <si>
+    <t>arloshultz@gmail.com</t>
+  </si>
+  <si>
     <t>shultz.miles@gmail.com</t>
-  </si>
-  <si>
-    <t>United States</t>
   </si>
   <si>
     <t>mileshultz@gmail.com</t>
@@ -55,7 +83,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -375,15 +403,15 @@
   </fills>
   <borders count="10">
     <border>
-      <left/>
-      <right/>
+      <start/>
+      <end/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <start/>
+      <end/>
       <top/>
       <bottom style="thick">
         <color theme="4"/>
@@ -391,8 +419,8 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <start/>
+      <end/>
       <top/>
       <bottom style="thick">
         <color theme="4" tint="0.499984740745262"/>
@@ -400,8 +428,8 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <start/>
+      <end/>
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.39997558519241921"/>
@@ -409,12 +437,12 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <start style="thin">
         <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
+      </start>
+      <end style="thin">
         <color rgb="FF7F7F7F"/>
-      </right>
+      </end>
       <top style="thin">
         <color rgb="FF7F7F7F"/>
       </top>
@@ -424,12 +452,12 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <start style="thin">
         <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
+      </start>
+      <end style="thin">
         <color rgb="FF3F3F3F"/>
-      </right>
+      </end>
       <top style="thin">
         <color rgb="FF3F3F3F"/>
       </top>
@@ -439,8 +467,8 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <start/>
+      <end/>
       <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
@@ -448,12 +476,12 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
+      <start style="double">
         <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
+      </start>
+      <end style="double">
         <color rgb="FF3F3F3F"/>
-      </right>
+      </end>
       <top style="double">
         <color rgb="FF3F3F3F"/>
       </top>
@@ -463,12 +491,12 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <start style="thin">
         <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
+      </start>
+      <end style="thin">
         <color rgb="FFB2B2B2"/>
-      </right>
+      </end>
       <top style="thin">
         <color rgb="FFB2B2B2"/>
       </top>
@@ -478,8 +506,8 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <start/>
+      <end/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -595,7 +623,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://purl.oclc.org/ooxml/drawingml/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -748,25 +776,25 @@
         </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
-            <a:gs pos="0">
+            <a:gs pos="0%">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:lumMod val="110%"/>
+                <a:satMod val="105%"/>
+                <a:tint val="67%"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="50%">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:lumMod val="105%"/>
+                <a:satMod val="103%"/>
+                <a:tint val="73%"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="100000">
+            <a:gs pos="100%">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:lumMod val="105%"/>
+                <a:satMod val="109%"/>
+                <a:tint val="81%"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -774,25 +802,25 @@
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
-            <a:gs pos="0">
+            <a:gs pos="0%">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:satMod val="103%"/>
+                <a:lumMod val="102%"/>
+                <a:tint val="94%"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="50%">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:satMod val="110%"/>
+                <a:lumMod val="100%"/>
+                <a:shade val="100%"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="100000">
+            <a:gs pos="100%">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:lumMod val="99%"/>
+                <a:satMod val="120%"/>
+                <a:shade val="78%"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -805,21 +833,21 @@
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
+          <a:miter lim="800%"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
+          <a:miter lim="800%"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
+          <a:miter lim="800%"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
@@ -833,7 +861,7 @@
           <a:effectLst>
             <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="63%"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
@@ -845,32 +873,32 @@
         </a:solidFill>
         <a:solidFill>
           <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
+            <a:tint val="95%"/>
+            <a:satMod val="170%"/>
           </a:schemeClr>
         </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
-            <a:gs pos="0">
+            <a:gs pos="0%">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="93%"/>
+                <a:satMod val="150%"/>
+                <a:shade val="98%"/>
+                <a:lumMod val="102%"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="50%">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="98%"/>
+                <a:satMod val="130%"/>
+                <a:shade val="90%"/>
+                <a:lumMod val="103%"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="100000">
+            <a:gs pos="100%">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="63%"/>
+                <a:satMod val="120%"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -910,13 +938,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C131944-8E32-3E4D-A250-0EAE9A5ECB01}">
-  <dimension ref="A1:F4"/>
+<worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{527E3337-65F4-2D4E-9DB6-07E16A1FE02D}">
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="21.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.33203125" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
@@ -951,8 +975,8 @@
       <c r="D2">
         <v>0</v>
       </c>
-      <c r="E2" s="1">
-        <v>46152.720578703702</v>
+      <c r="E2" s="1" t="d">
+        <v>2026-06-18T16:59:28.99999987799673975</v>
       </c>
       <c r="F2" t="s">
         <v>7</v>
@@ -971,8 +995,8 @@
       <c r="D3">
         <v>0</v>
       </c>
-      <c r="E3" s="1">
-        <v>46151.732754629629</v>
+      <c r="E3" s="1" t="d">
+        <v>2026-06-18T12:14:13.00000011920929050</v>
       </c>
       <c r="F3" t="s">
         <v>7</v>
@@ -991,8 +1015,88 @@
       <c r="D4">
         <v>0</v>
       </c>
-      <c r="E4" s="1">
-        <v>46151.723252314812</v>
+      <c r="E4" s="1" t="d">
+        <v>2026-05-20T18:00:55.000000284053384925</v>
+      </c>
+      <c r="F4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5" s="1" t="d">
+        <v>2026-05-16T17:13:46.99999990873038675</v>
+      </c>
+      <c r="F5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6" s="1" t="d">
+        <v>2026-05-10T17:17:37.99999984446912975</v>
+      </c>
+      <c r="F6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7" s="1" t="d">
+        <v>2026-05-09T17:35:09.99999996274709925</v>
+      </c>
+      <c r="F7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8" s="1" t="d">
+        <v>2026-05-09T17:21:28.99999978020787275</v>
       </c>
     </row>
   </sheetData>

--- a/docs/resources/mailing_list.xlsx
+++ b/docs/resources/mailing_list.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/milesshultz/Documents/kings_website/rock/docs/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{30C6D1EF-AB46-2948-BD17-DD8C503A3731}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0A5C3DB0-D2DE-D64B-8FE1-97A889ABB90B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5580" yWindow="2380" windowWidth="27640" windowHeight="16680" xr2:uid="{DA709F05-24F1-A741-ABB1-68CCE26981F7}"/>
+    <workbookView xWindow="5560" yWindow="2380" windowWidth="27640" windowHeight="16680" xr2:uid="{89E61C59-7AC5-574C-B30B-74417DA03217}"/>
   </bookViews>
   <sheets>
-    <sheet name="1781904772_190740977600693589_s" sheetId="1" r:id="rId1"/>
+    <sheet name="1782051151_190894467913352744_s" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="19" uniqueCount="14">
+<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="21" uniqueCount="15">
   <si>
     <t>Subscriber</t>
   </si>
@@ -56,10 +56,13 @@
     <t>Location</t>
   </si>
   <si>
+    <t>lroderick26@gmail.com</t>
+  </si>
+  <si>
+    <t>United States</t>
+  </si>
+  <si>
     <t>monicagchavez@gmail.com</t>
-  </si>
-  <si>
-    <t>United States</t>
   </si>
   <si>
     <t>rachel.chasse21@gmail.com</t>
@@ -938,9 +941,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{527E3337-65F4-2D4E-9DB6-07E16A1FE02D}">
-  <dimension ref="A1:F8"/>
+<worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCC26F75-3205-4447-AA82-B8FDD6496211}">
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="24.83203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
@@ -976,7 +982,7 @@
         <v>0</v>
       </c>
       <c r="E2" s="1" t="d">
-        <v>2026-06-18T16:59:28.99999987799673975</v>
+        <v>2026-06-20T17:58:38.99999992456287075</v>
       </c>
       <c r="F2" t="s">
         <v>7</v>
@@ -996,7 +1002,7 @@
         <v>0</v>
       </c>
       <c r="E3" s="1" t="d">
-        <v>2026-06-18T12:14:13.00000011920929050</v>
+        <v>2026-06-18T16:59:28.99999987799673975</v>
       </c>
       <c r="F3" t="s">
         <v>7</v>
@@ -1016,7 +1022,7 @@
         <v>0</v>
       </c>
       <c r="E4" s="1" t="d">
-        <v>2026-05-20T18:00:55.000000284053384925</v>
+        <v>2026-06-18T12:14:13.00000011920929050</v>
       </c>
       <c r="F4" t="s">
         <v>7</v>
@@ -1036,7 +1042,7 @@
         <v>0</v>
       </c>
       <c r="E5" s="1" t="d">
-        <v>2026-05-16T17:13:46.99999990873038675</v>
+        <v>2026-05-20T18:00:55.000000284053384925</v>
       </c>
       <c r="F5" t="s">
         <v>7</v>
@@ -1056,7 +1062,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="1" t="d">
-        <v>2026-05-10T17:17:37.99999984446912975</v>
+        <v>2026-05-16T17:13:46.99999990873038675</v>
       </c>
       <c r="F6" t="s">
         <v>7</v>
@@ -1076,7 +1082,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="1" t="d">
-        <v>2026-05-09T17:35:09.99999996274709925</v>
+        <v>2026-05-10T17:17:37.99999984446912975</v>
       </c>
       <c r="F7" t="s">
         <v>7</v>
@@ -1096,6 +1102,26 @@
         <v>0</v>
       </c>
       <c r="E8" s="1" t="d">
+        <v>2026-05-09T17:35:09.99999996274709925</v>
+      </c>
+      <c r="F8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9">
+        <v>0</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9" s="1" t="d">
         <v>2026-05-09T17:21:28.99999978020787275</v>
       </c>
     </row>

--- a/docs/resources/mailing_list.xlsx
+++ b/docs/resources/mailing_list.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/milesshultz/Documents/kings_website/rock/docs/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0A5C3DB0-D2DE-D64B-8FE1-97A889ABB90B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{F6D1B5D4-B546-1347-8B75-C3D8491D2E11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5560" yWindow="2380" windowWidth="27640" windowHeight="16680" xr2:uid="{89E61C59-7AC5-574C-B30B-74417DA03217}"/>
+    <workbookView xWindow="5540" yWindow="2340" windowWidth="27640" windowHeight="16680" xr2:uid="{43B202D6-C586-9347-AB4D-F21FE8637ED4}"/>
   </bookViews>
   <sheets>
-    <sheet name="1782051151_190894467913352744_s" sheetId="1" r:id="rId1"/>
+    <sheet name="1782071473_190915777586530245_s" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="21" uniqueCount="15">
+<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="28" uniqueCount="21">
   <si>
     <t>Subscriber</t>
   </si>
@@ -62,6 +62,9 @@
     <t>United States</t>
   </si>
   <si>
+    <t>treehugger.aj@gmail.com</t>
+  </si>
+  <si>
     <t>monicagchavez@gmail.com</t>
   </si>
   <si>
@@ -81,13 +84,28 @@
   </si>
   <si>
     <t>kingsofewing@gmail.com</t>
+  </si>
+  <si>
+    <t>jean.clipperton@gmail.com</t>
+  </si>
+  <si>
+    <t>Andgreene11@gmail.com</t>
+  </si>
+  <si>
+    <t>mattstork1@gmail.com</t>
+  </si>
+  <si>
+    <t>jacri3@comcast.net</t>
+  </si>
+  <si>
+    <t>jackwestwood@gmail.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -218,6 +236,14 @@
     <font>
       <sz val="12"/>
       <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -520,7 +546,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="42">
+  <cellStyleXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
@@ -563,12 +589,14 @@
     <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="42"/>
   </cellXfs>
-  <cellStyles count="42">
+  <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
     <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
     <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
@@ -602,6 +630,7 @@
     <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
     <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
     <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Hyperlink" xfId="42" builtinId="8"/>
     <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
     <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
     <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
@@ -941,11 +970,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCC26F75-3205-4447-AA82-B8FDD6496211}">
-  <dimension ref="A1:F9"/>
+<worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5AA3B81-CD4B-574C-A73A-FB479EB57C44}">
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
@@ -969,108 +999,33 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2">
-        <v>0</v>
-      </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-      <c r="E2" s="1" t="d">
-        <v>2026-06-20T17:58:38.99999992456287075</v>
-      </c>
-      <c r="F2" t="s">
-        <v>7</v>
+      <c r="A2" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3">
-        <v>0</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-      <c r="E3" s="1" t="d">
-        <v>2026-06-18T16:59:28.99999987799673975</v>
-      </c>
-      <c r="F3" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4">
-        <v>0</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4" s="1" t="d">
-        <v>2026-06-18T12:14:13.00000011920929050</v>
-      </c>
-      <c r="F4" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5">
-        <v>0</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-      <c r="E5" s="1" t="d">
-        <v>2026-05-20T18:00:55.000000284053384925</v>
-      </c>
-      <c r="F5" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6">
-        <v>0</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6" s="1" t="d">
-        <v>2026-05-16T17:13:46.99999990873038675</v>
-      </c>
-      <c r="F6" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1082,15 +1037,12 @@
         <v>0</v>
       </c>
       <c r="E7" s="1" t="d">
-        <v>2026-05-10T17:17:37.99999984446912975</v>
-      </c>
-      <c r="F7" t="s">
-        <v>7</v>
+        <v>2026-05-09T17:21:28.99999978020787275</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -1110,7 +1062,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1122,10 +1074,139 @@
         <v>0</v>
       </c>
       <c r="E9" s="1" t="d">
-        <v>2026-05-09T17:21:28.99999978020787275</v>
+        <v>2026-05-10T17:17:37.99999984446912975</v>
+      </c>
+      <c r="F9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10" s="1" t="d">
+        <v>2026-05-16T17:13:46.99999990873038675</v>
+      </c>
+      <c r="F10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11">
+        <v>0</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11" s="1" t="d">
+        <v>2026-05-20T18:00:55.000000284053384925</v>
+      </c>
+      <c r="F11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12">
+        <v>0</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12" s="1" t="d">
+        <v>2026-06-18T12:14:13.00000011920929050</v>
+      </c>
+      <c r="F12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13">
+        <v>0</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13" s="1" t="d">
+        <v>2026-06-18T16:59:28.99999987799673975</v>
+      </c>
+      <c r="F13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>6</v>
+      </c>
+      <c r="B14">
+        <v>0</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14" s="1" t="d">
+        <v>2026-06-20T17:58:38.99999992456287075</v>
+      </c>
+      <c r="F14" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>8</v>
+      </c>
+      <c r="B15">
+        <v>0</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15" s="1" t="d">
+        <v>2026-06-21T15:34:35.999999977648258200</v>
+      </c>
+      <c r="F15" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F15">
+    <sortCondition ref="E7:E15"/>
+  </sortState>
+  <hyperlinks>
+    <hyperlink ref="A2" r:id="rId1" xr:uid="{7C5D4C31-43E7-6E4C-8EC0-2D0D5BDCE70A}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/resources/mailing_list.xlsx
+++ b/docs/resources/mailing_list.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/milesshultz/Documents/kings_website/rock/docs/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{F6D1B5D4-B546-1347-8B75-C3D8491D2E11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{CA63021E-19BB-C342-9A5D-250D1843A044}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5540" yWindow="2340" windowWidth="27640" windowHeight="16680" xr2:uid="{43B202D6-C586-9347-AB4D-F21FE8637ED4}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="28" uniqueCount="21">
+<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="32" uniqueCount="25">
   <si>
     <t>Subscriber</t>
   </si>
@@ -99,6 +99,18 @@
   </si>
   <si>
     <t>jackwestwood@gmail.com</t>
+  </si>
+  <si>
+    <t>august.shultz@gmail.com</t>
+  </si>
+  <si>
+    <t>morrison.shultz@gmail.com</t>
+  </si>
+  <si>
+    <t>ritaswales@hotmail.com</t>
+  </si>
+  <si>
+    <t>ethanmmc@gmail.com</t>
   </si>
 </sst>
 </file>
@@ -971,7 +983,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5AA3B81-CD4B-574C-A73A-FB479EB57C44}">
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.83203125" bestFit="1" customWidth="1"/>
@@ -999,110 +1011,53 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" s="2" t="s">
-        <v>16</v>
+      <c r="A2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>20</v>
+      <c r="A6" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7">
-        <v>0</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7" s="1" t="d">
-        <v>2026-05-09T17:21:28.99999978020787275</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8">
-        <v>0</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8" s="1" t="d">
-        <v>2026-05-09T17:35:09.99999996274709925</v>
-      </c>
-      <c r="F8" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9">
-        <v>0</v>
-      </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9" s="1" t="d">
-        <v>2026-05-10T17:17:37.99999984446912975</v>
-      </c>
-      <c r="F9" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10">
-        <v>0</v>
-      </c>
-      <c r="C10">
-        <v>0</v>
-      </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10" s="1" t="d">
-        <v>2026-05-16T17:13:46.99999990873038675</v>
-      </c>
-      <c r="F10" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -1114,15 +1069,12 @@
         <v>0</v>
       </c>
       <c r="E11" s="1" t="d">
-        <v>2026-05-20T18:00:55.000000284053384925</v>
-      </c>
-      <c r="F11" t="s">
-        <v>7</v>
+        <v>2026-05-09T17:21:28.99999978020787275</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -1134,7 +1086,7 @@
         <v>0</v>
       </c>
       <c r="E12" s="1" t="d">
-        <v>2026-06-18T12:14:13.00000011920929050</v>
+        <v>2026-05-09T17:35:09.99999996274709925</v>
       </c>
       <c r="F12" t="s">
         <v>7</v>
@@ -1142,7 +1094,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -1154,7 +1106,7 @@
         <v>0</v>
       </c>
       <c r="E13" s="1" t="d">
-        <v>2026-06-18T16:59:28.99999987799673975</v>
+        <v>2026-05-10T17:17:37.99999984446912975</v>
       </c>
       <c r="F13" t="s">
         <v>7</v>
@@ -1162,7 +1114,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -1174,7 +1126,7 @@
         <v>0</v>
       </c>
       <c r="E14" s="1" t="d">
-        <v>2026-06-20T17:58:38.99999992456287075</v>
+        <v>2026-05-16T17:13:46.99999990873038675</v>
       </c>
       <c r="F14" t="s">
         <v>7</v>
@@ -1182,7 +1134,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -1194,18 +1146,98 @@
         <v>0</v>
       </c>
       <c r="E15" s="1" t="d">
-        <v>2026-06-21T15:34:35.999999977648258200</v>
+        <v>2026-05-20T18:00:55.000000284053384925</v>
       </c>
       <c r="F15" t="s">
         <v>7</v>
       </c>
     </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>10</v>
+      </c>
+      <c r="B16">
+        <v>0</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16" s="1" t="d">
+        <v>2026-06-18T12:14:13.00000011920929050</v>
+      </c>
+      <c r="F16" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17">
+        <v>0</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17" s="1" t="d">
+        <v>2026-06-18T16:59:28.99999987799673975</v>
+      </c>
+      <c r="F17" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>6</v>
+      </c>
+      <c r="B18">
+        <v>0</v>
+      </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18" s="1" t="d">
+        <v>2026-06-20T17:58:38.99999992456287075</v>
+      </c>
+      <c r="F18" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>8</v>
+      </c>
+      <c r="B19">
+        <v>0</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19" s="1" t="d">
+        <v>2026-06-21T15:34:35.999999977648258200</v>
+      </c>
+      <c r="F19" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F15">
-    <sortCondition ref="E7:E15"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A6:F19">
+    <sortCondition ref="E11:E19"/>
   </sortState>
   <hyperlinks>
-    <hyperlink ref="A2" r:id="rId1" xr:uid="{7C5D4C31-43E7-6E4C-8EC0-2D0D5BDCE70A}"/>
+    <hyperlink ref="A6" r:id="rId1" xr:uid="{7C5D4C31-43E7-6E4C-8EC0-2D0D5BDCE70A}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
